--- a/data/Heat map 5.xlsx
+++ b/data/Heat map 5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB6EAC8-AC86-4F10-801A-350B01AC7F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B2B48F-ED00-4AF9-A084-492253E38B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9DC939E2-9D2B-49F9-96FE-7432C9E71486}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>KPI by Nr.</t>
   </si>
@@ -48,101 +51,100 @@
     <t>Society Impact &amp; Inclusion</t>
   </si>
   <si>
-    <t>ARIs collaborations</t>
+    <t>GI</t>
+  </si>
+  <si>
+    <t>Biotech</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Breeding</t>
+  </si>
+  <si>
+    <t>Genebanks</t>
+  </si>
+  <si>
+    <t>Seed System</t>
+  </si>
+  <si>
+    <t>RAFS</t>
+  </si>
+  <si>
+    <t>Plant Health</t>
+  </si>
+  <si>
+    <t>Farming Systems Agronomy</t>
+  </si>
+  <si>
+    <t>Mechanization</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>2025 Actual Values</t>
+  </si>
+  <si>
+    <t>Annual Target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per Program Target </t>
+  </si>
+  <si>
+    <t>Natural Resource Management</t>
+  </si>
+  <si>
+    <t>Foresight &amp; Impact Assessment</t>
+  </si>
+  <si>
+    <t>Gender, Youth &amp; Social Inclusion</t>
+  </si>
+  <si>
+    <t>Reslience &amp; Climate Adaptation</t>
+  </si>
+  <si>
+    <t>Nutrition and Health</t>
+  </si>
+  <si>
+    <t>Value Chain Markets and Agribusiness</t>
+  </si>
+  <si>
+    <t>Collaboration with Agriculture Research Institutions</t>
   </si>
   <si>
     <t>Active collaborations with scaling partners</t>
   </si>
   <si>
-    <t>Awards grated to IITA stafff</t>
-  </si>
-  <si>
-    <t>Invitations to give seminars/talks</t>
+    <t>Awards granted to IITA staff or project teams</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Invitations for presentations or seminars</t>
   </si>
   <si>
     <t>High level engagements</t>
   </si>
   <si>
-    <t>Approved proposals with GeYSI components</t>
+    <t xml:space="preserve"> Approved proposals with GeYSI components</t>
   </si>
   <si>
     <t>Approved proposals with climate components</t>
   </si>
   <si>
-    <t>Approved proposals with nutrition and health components</t>
-  </si>
-  <si>
-    <t>GI</t>
-  </si>
-  <si>
-    <t>Biotech</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Breeding</t>
-  </si>
-  <si>
-    <t>Genebanks</t>
-  </si>
-  <si>
-    <t>Seed System</t>
-  </si>
-  <si>
-    <t>RAFS</t>
-  </si>
-  <si>
-    <t>Plant Health</t>
-  </si>
-  <si>
-    <t>Farming Systems Agronomy</t>
-  </si>
-  <si>
-    <t>NRM</t>
-  </si>
-  <si>
-    <t>Mechanization</t>
-  </si>
-  <si>
-    <t>ST</t>
-  </si>
-  <si>
-    <t>FIAS</t>
-  </si>
-  <si>
-    <t>GeYSI</t>
-  </si>
-  <si>
-    <t>RCA</t>
-  </si>
-  <si>
-    <t>Nutrition</t>
-  </si>
-  <si>
-    <t>VCMA</t>
-  </si>
-  <si>
-    <t>2025 Actual Values</t>
-  </si>
-  <si>
-    <t>Annual Target</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per Program Target </t>
+    <t>Approved proposals with nutrition ad health components</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,20 +162,6 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -205,15 +193,8 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF00B050"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -221,21 +202,20 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF0070C0"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="Aptos Narrow"/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -248,8 +228,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -276,6 +262,19 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -428,15 +427,86 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF00B050"/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -444,22 +514,11 @@
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
       <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
+        <color theme="1"/>
       </top>
       <bottom style="thin">
         <color indexed="64"/>
@@ -470,19 +529,8 @@
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="medium">
+        <color theme="1"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
@@ -496,63 +544,37 @@
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -561,253 +583,207 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF00B050"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="17" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3" xr:uid="{8F5BA9A4-0180-472C-9FA0-1AB0EADDA468}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
-    <cellStyle name="Percent 2" xfId="4" xr:uid="{AB8EF1BB-5864-448F-A670-6049F275543A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1138,649 +1114,626 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32992BCD-9E8C-46B8-AAEF-2DC1F617F4CB}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:AB19"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.21875" style="25" customWidth="1"/>
-    <col min="2" max="2" width="3.21875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.77734375" style="33" customWidth="1"/>
-    <col min="4" max="5" width="9.77734375" style="48" customWidth="1"/>
-    <col min="6" max="6" width="9.77734375" style="49" customWidth="1"/>
-    <col min="7" max="11" width="9.77734375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="3.21875" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" style="21" customWidth="1"/>
+    <col min="4" max="5" width="9.77734375" style="44" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" style="45" customWidth="1"/>
+    <col min="7" max="11" width="9.77734375" style="18" customWidth="1"/>
     <col min="12" max="12" width="5.6640625" style="2" customWidth="1"/>
     <col min="13" max="14" width="8.21875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
+    <row r="1" spans="2:14" ht="15" thickBot="1">
       <c r="B1" s="1"/>
-      <c r="C1" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="52"/>
+      <c r="C1" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="62"/>
     </row>
-    <row r="2" spans="1:14" s="8" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4"/>
+    <row r="2" spans="2:14" s="7" customFormat="1" ht="25.95" customHeight="1" thickBot="1">
       <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="58" t="s">
+      <c r="C2" s="46"/>
+      <c r="D2" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="53" t="s">
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="51"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="18" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
+    <row r="3" spans="2:14" s="17" customFormat="1" ht="132" customHeight="1" thickBot="1">
       <c r="B3" s="1"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="15"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+    </row>
+    <row r="4" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B4" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="C4" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="D4" s="36">
+        <v>17</v>
+      </c>
+      <c r="E4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="F4" s="37">
+        <v>1</v>
+      </c>
+      <c r="G4" s="37">
+        <v>0</v>
+      </c>
+      <c r="H4" s="38"/>
+      <c r="I4" s="47">
+        <v>0</v>
+      </c>
+      <c r="J4" s="48">
+        <v>0</v>
+      </c>
+      <c r="K4" s="49">
+        <v>0</v>
+      </c>
+      <c r="L4" s="18"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+    </row>
+    <row r="5" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B5" s="57"/>
+      <c r="C5" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="D5" s="36">
+        <v>23</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="37">
+        <v>0</v>
+      </c>
+      <c r="G5" s="37">
+        <v>3</v>
+      </c>
+      <c r="H5" s="38"/>
+      <c r="I5" s="50">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J5" s="51">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K5" s="49">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L5" s="18"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+    </row>
+    <row r="6" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B6" s="57"/>
+      <c r="C6" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="D6" s="36">
+        <v>19</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="37">
+        <v>0</v>
+      </c>
+      <c r="G6" s="37">
+        <v>1</v>
+      </c>
+      <c r="H6" s="38"/>
+      <c r="I6" s="50">
+        <v>0</v>
+      </c>
+      <c r="J6" s="51">
+        <v>0</v>
+      </c>
+      <c r="K6" s="52">
+        <v>0</v>
+      </c>
+      <c r="L6" s="18"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+    </row>
+    <row r="7" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B7" s="58"/>
+      <c r="C7" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="D7" s="36">
+        <v>0</v>
+      </c>
+      <c r="E7" s="37">
+        <v>14</v>
+      </c>
+      <c r="F7" s="37">
+        <v>3</v>
+      </c>
+      <c r="G7" s="37">
+        <v>0</v>
+      </c>
+      <c r="H7" s="38"/>
+      <c r="I7" s="53">
+        <v>0.43</v>
+      </c>
+      <c r="J7" s="54">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="K7" s="55">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L7" s="18"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+    </row>
+    <row r="8" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B8" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="C8" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="16"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
+      <c r="D8" s="36">
+        <v>18</v>
+      </c>
+      <c r="E8" s="37">
+        <v>1</v>
+      </c>
+      <c r="F8" s="37">
+        <v>3</v>
+      </c>
+      <c r="G8" s="37">
+        <v>5</v>
+      </c>
+      <c r="H8" s="38"/>
+      <c r="I8" s="47">
+        <v>0.33</v>
+      </c>
+      <c r="J8" s="48">
+        <v>0.33</v>
+      </c>
+      <c r="K8" s="49">
+        <v>0</v>
+      </c>
+      <c r="L8" s="18"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
     </row>
-    <row r="4" spans="1:14" s="25" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="55" t="s">
+    <row r="9" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B9" s="57"/>
+      <c r="C9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="D9" s="36">
+        <v>43</v>
+      </c>
+      <c r="E9" s="37">
+        <v>17</v>
+      </c>
+      <c r="F9" s="37">
+        <v>0</v>
+      </c>
+      <c r="G9" s="37">
+        <v>3</v>
+      </c>
+      <c r="H9" s="38"/>
+      <c r="I9" s="50">
+        <v>0.44</v>
+      </c>
+      <c r="J9" s="51">
+        <v>0.44</v>
+      </c>
+      <c r="K9" s="55">
+        <v>0.11</v>
+      </c>
+      <c r="L9" s="18"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+    </row>
+    <row r="10" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B10" s="57"/>
+      <c r="C10" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="36">
+        <v>0</v>
+      </c>
+      <c r="E10" s="37">
+        <v>3</v>
+      </c>
+      <c r="F10" s="37">
+        <v>0</v>
+      </c>
+      <c r="G10" s="37">
+        <v>0</v>
+      </c>
+      <c r="H10" s="38"/>
+      <c r="I10" s="50">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J10" s="51">
+        <v>0.71</v>
+      </c>
+      <c r="K10" s="52">
+        <v>0</v>
+      </c>
+      <c r="L10" s="18"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+    </row>
+    <row r="11" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B11" s="58"/>
+      <c r="C11" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="20">
-        <v>17</v>
-      </c>
-      <c r="E4" s="21" t="s">
+      <c r="D11" s="36">
+        <v>0</v>
+      </c>
+      <c r="E11" s="37">
+        <v>0</v>
+      </c>
+      <c r="F11" s="37">
+        <v>0</v>
+      </c>
+      <c r="G11" s="37">
+        <v>0</v>
+      </c>
+      <c r="H11" s="38"/>
+      <c r="I11" s="53">
+        <v>0</v>
+      </c>
+      <c r="J11" s="54">
+        <v>0</v>
+      </c>
+      <c r="K11" s="55">
+        <v>0</v>
+      </c>
+      <c r="L11" s="18"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+    </row>
+    <row r="12" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B12" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="21">
+      <c r="C12" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="36">
+        <v>7</v>
+      </c>
+      <c r="E12" s="39">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39">
+        <v>0</v>
+      </c>
+      <c r="G12" s="37">
+        <v>0</v>
+      </c>
+      <c r="H12" s="38"/>
+      <c r="I12" s="47">
+        <v>0</v>
+      </c>
+      <c r="J12" s="48">
+        <v>0</v>
+      </c>
+      <c r="K12" s="49">
+        <v>0</v>
+      </c>
+      <c r="L12" s="18"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+    </row>
+    <row r="13" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B13" s="57"/>
+      <c r="C13" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="36">
+        <v>0</v>
+      </c>
+      <c r="E13" s="39">
+        <v>0</v>
+      </c>
+      <c r="F13" s="39">
+        <v>0</v>
+      </c>
+      <c r="G13" s="37">
+        <v>3</v>
+      </c>
+      <c r="H13" s="38"/>
+      <c r="I13" s="50">
+        <v>0</v>
+      </c>
+      <c r="J13" s="51">
+        <v>0</v>
+      </c>
+      <c r="K13" s="52">
+        <v>0</v>
+      </c>
+      <c r="L13" s="18"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+    </row>
+    <row r="14" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B14" s="57"/>
+      <c r="C14" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="36">
+        <v>6</v>
+      </c>
+      <c r="E14" s="39">
+        <v>3</v>
+      </c>
+      <c r="F14" s="39">
+        <v>0</v>
+      </c>
+      <c r="G14" s="37">
+        <v>3</v>
+      </c>
+      <c r="H14" s="38"/>
+      <c r="I14" s="50">
+        <v>0</v>
+      </c>
+      <c r="J14" s="51">
+        <v>0</v>
+      </c>
+      <c r="K14" s="52">
+        <v>0</v>
+      </c>
+      <c r="L14" s="18"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+    </row>
+    <row r="15" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B15" s="57"/>
+      <c r="C15" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="36">
+        <v>7</v>
+      </c>
+      <c r="E15" s="39">
+        <v>0</v>
+      </c>
+      <c r="F15" s="39">
+        <v>0</v>
+      </c>
+      <c r="G15" s="37">
+        <v>0</v>
+      </c>
+      <c r="H15" s="38"/>
+      <c r="I15" s="50">
+        <v>0</v>
+      </c>
+      <c r="J15" s="51">
+        <v>0</v>
+      </c>
+      <c r="K15" s="52">
+        <v>0</v>
+      </c>
+      <c r="L15" s="18"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+    </row>
+    <row r="16" spans="2:14" s="20" customFormat="1" ht="15.45" customHeight="1" thickBot="1">
+      <c r="B16" s="58"/>
+      <c r="C16" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="40">
+        <v>0</v>
+      </c>
+      <c r="E16" s="41">
+        <v>0</v>
+      </c>
+      <c r="F16" s="41">
         <v>1</v>
       </c>
-      <c r="G4" s="21">
-        <v>0</v>
-      </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="63">
-        <v>0</v>
-      </c>
-      <c r="J4" s="64">
-        <v>0</v>
-      </c>
-      <c r="K4" s="65">
-        <v>0</v>
-      </c>
-      <c r="L4" s="23"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
+      <c r="G16" s="42">
+        <v>0</v>
+      </c>
+      <c r="H16" s="43"/>
+      <c r="I16" s="53">
+        <v>1</v>
+      </c>
+      <c r="J16" s="54">
+        <v>0</v>
+      </c>
+      <c r="K16" s="55">
+        <v>0</v>
+      </c>
+      <c r="L16" s="18"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
     </row>
-    <row r="5" spans="1:14" s="25" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="26" t="s">
+    <row r="17" spans="2:28" s="31" customFormat="1" ht="12">
+      <c r="B17" s="26"/>
+      <c r="C17" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="20">
-        <v>23</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="21">
-        <v>0</v>
-      </c>
-      <c r="G5" s="21">
-        <v>3</v>
-      </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="66">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="J5" s="67">
-        <v>2.7777777777777776E-2</v>
-      </c>
-      <c r="K5" s="65">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="L5" s="23"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-    </row>
-    <row r="6" spans="1:14" s="25" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="20">
-        <v>19</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="21">
-        <v>0</v>
-      </c>
-      <c r="G6" s="21">
-        <v>1</v>
-      </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="66">
-        <v>0</v>
-      </c>
-      <c r="J6" s="67">
-        <v>0</v>
-      </c>
-      <c r="K6" s="68">
-        <v>0</v>
-      </c>
-      <c r="L6" s="23"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-    </row>
-    <row r="7" spans="1:14" s="25" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="20">
-        <v>0</v>
-      </c>
-      <c r="E7" s="21">
-        <v>14</v>
-      </c>
-      <c r="F7" s="21">
-        <v>3</v>
-      </c>
-      <c r="G7" s="21">
-        <v>0</v>
-      </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="69">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="J7" s="70">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K7" s="71">
-        <v>2.7777777777777776E-2</v>
-      </c>
-      <c r="L7" s="23"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-    </row>
-    <row r="8" spans="1:14" s="25" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="20">
-        <v>18</v>
-      </c>
-      <c r="E8" s="21">
-        <v>1</v>
-      </c>
-      <c r="F8" s="21">
-        <v>3</v>
-      </c>
-      <c r="G8" s="21">
-        <v>5</v>
-      </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="63">
-        <v>2.7777777777777776E-2</v>
-      </c>
-      <c r="J8" s="64">
-        <v>2.7777777777777776E-2</v>
-      </c>
-      <c r="K8" s="65">
-        <v>0</v>
-      </c>
-      <c r="L8" s="23"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24"/>
-    </row>
-    <row r="9" spans="1:14" s="25" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="56"/>
-      <c r="C9" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="20">
-        <v>43</v>
-      </c>
-      <c r="E9" s="21">
-        <v>17</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0</v>
-      </c>
-      <c r="G9" s="21">
-        <v>3</v>
-      </c>
-      <c r="H9" s="22"/>
-      <c r="I9" s="66">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="J9" s="67">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="K9" s="71">
-        <v>2.7777777777777776E-2</v>
-      </c>
-      <c r="L9" s="23"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="24"/>
-    </row>
-    <row r="10" spans="1:14" s="25" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="56"/>
-      <c r="C10" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="20">
-        <v>0</v>
-      </c>
-      <c r="E10" s="21">
-        <v>3</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0</v>
-      </c>
-      <c r="G10" s="21">
-        <v>0</v>
-      </c>
-      <c r="H10" s="22"/>
-      <c r="I10" s="66">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="J10" s="67">
-        <v>0.1388888888888889</v>
-      </c>
-      <c r="K10" s="68">
-        <v>0</v>
-      </c>
-      <c r="L10" s="23"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-    </row>
-    <row r="11" spans="1:14" s="25" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="20">
-        <v>0</v>
-      </c>
-      <c r="E11" s="21">
-        <v>0</v>
-      </c>
-      <c r="F11" s="21">
-        <v>0</v>
-      </c>
-      <c r="G11" s="21">
-        <v>0</v>
-      </c>
-      <c r="H11" s="22"/>
-      <c r="I11" s="69">
-        <v>0</v>
-      </c>
-      <c r="J11" s="70">
-        <v>0</v>
-      </c>
-      <c r="K11" s="71">
-        <v>0</v>
-      </c>
-      <c r="L11" s="23"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
-    </row>
-    <row r="12" spans="1:14" s="25" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="20">
-        <v>7</v>
-      </c>
-      <c r="E12" s="30">
-        <v>0</v>
-      </c>
-      <c r="F12" s="30">
-        <v>0</v>
-      </c>
-      <c r="G12" s="21">
-        <v>0</v>
-      </c>
-      <c r="H12" s="22"/>
-      <c r="I12" s="63">
-        <v>0</v>
-      </c>
-      <c r="J12" s="64">
-        <v>0</v>
-      </c>
-      <c r="K12" s="65">
-        <v>0</v>
-      </c>
-      <c r="L12" s="23"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-    </row>
-    <row r="13" spans="1:14" s="25" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="56"/>
-      <c r="C13" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="20">
-        <v>0</v>
-      </c>
-      <c r="E13" s="30">
-        <v>0</v>
-      </c>
-      <c r="F13" s="30">
-        <v>0</v>
-      </c>
-      <c r="G13" s="21">
-        <v>3</v>
-      </c>
-      <c r="H13" s="22"/>
-      <c r="I13" s="66">
-        <v>0</v>
-      </c>
-      <c r="J13" s="67">
-        <v>0</v>
-      </c>
-      <c r="K13" s="68">
-        <v>0</v>
-      </c>
-      <c r="L13" s="23"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-    </row>
-    <row r="14" spans="1:14" s="25" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="20">
-        <v>6</v>
-      </c>
-      <c r="E14" s="30">
-        <v>3</v>
-      </c>
-      <c r="F14" s="30">
-        <v>0</v>
-      </c>
-      <c r="G14" s="21">
-        <v>3</v>
-      </c>
-      <c r="H14" s="22"/>
-      <c r="I14" s="66">
-        <v>0</v>
-      </c>
-      <c r="J14" s="67">
-        <v>0</v>
-      </c>
-      <c r="K14" s="68">
-        <v>0</v>
-      </c>
-      <c r="L14" s="23"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-    </row>
-    <row r="15" spans="1:14" s="25" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="20">
-        <v>7</v>
-      </c>
-      <c r="E15" s="30">
-        <v>0</v>
-      </c>
-      <c r="F15" s="30">
-        <v>0</v>
-      </c>
-      <c r="G15" s="21">
-        <v>0</v>
-      </c>
-      <c r="H15" s="22"/>
-      <c r="I15" s="66">
-        <v>0</v>
-      </c>
-      <c r="J15" s="67">
-        <v>0</v>
-      </c>
-      <c r="K15" s="68">
-        <v>0</v>
-      </c>
-      <c r="L15" s="23"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-    </row>
-    <row r="16" spans="1:14" s="25" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="62"/>
-      <c r="C16" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="31">
-        <v>0</v>
-      </c>
-      <c r="E16" s="32">
-        <v>0</v>
-      </c>
-      <c r="F16" s="32">
-        <v>1</v>
-      </c>
-      <c r="G16" s="28">
-        <v>0</v>
-      </c>
-      <c r="H16" s="29"/>
-      <c r="I16" s="69">
-        <v>2.7777777777777776E-2</v>
-      </c>
-      <c r="J16" s="70">
-        <v>0</v>
-      </c>
-      <c r="K16" s="71">
-        <v>0</v>
-      </c>
-      <c r="L16" s="23"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-    </row>
-    <row r="17" spans="1:28" s="39" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="34"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="36">
+      <c r="D17" s="28">
         <f>SUM(D4:D16)</f>
         <v>140</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="28">
         <f>SUM(E4:E16)</f>
         <v>38</v>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="28">
         <f>SUM(F4:F16)</f>
         <v>8</v>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="28">
         <f>SUM(G4:G16)</f>
         <v>18</v>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="28">
         <v>30</v>
       </c>
-      <c r="I17" s="37">
-        <f>SUM(I4:I16)</f>
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J17" s="37">
-        <f>SUM(J4:J16)</f>
-        <v>0.3611111111111111</v>
-      </c>
-      <c r="K17" s="37">
-        <f>SUM(K4:K16)</f>
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="L17" s="38"/>
+      <c r="I17" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="30"/>
     </row>
-    <row r="18" spans="1:28" s="46" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="42">
+    <row r="18" spans="2:28" s="34" customFormat="1">
+      <c r="B18" s="32"/>
+      <c r="C18" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="28">
         <v>30</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="27">
         <v>25</v>
       </c>
-      <c r="F18" s="42">
+      <c r="F18" s="28">
         <v>30</v>
       </c>
-      <c r="G18" s="42">
+      <c r="G18" s="28">
         <v>30</v>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="27">
         <v>15</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="29">
         <v>0.25</v>
       </c>
-      <c r="J18" s="43">
+      <c r="J18" s="29">
         <v>0.25</v>
       </c>
-      <c r="K18" s="43">
+      <c r="K18" s="29">
         <v>0.25</v>
       </c>
-      <c r="L18" s="44"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
     </row>
-    <row r="19" spans="1:28" s="46" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="47">
+    <row r="19" spans="2:28" s="34" customFormat="1">
+      <c r="B19" s="32"/>
+      <c r="C19" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="35">
         <f>D18/13</f>
         <v>2.3076923076923075</v>
       </c>
-      <c r="E19" s="47">
-        <f>E18/13</f>
+      <c r="E19" s="35">
+        <f t="shared" ref="E19:G19" si="0">E18/13</f>
         <v>1.9230769230769231</v>
       </c>
-      <c r="F19" s="47">
-        <f>F18/13</f>
+      <c r="F19" s="35">
+        <f t="shared" si="0"/>
         <v>2.3076923076923075</v>
       </c>
-      <c r="G19" s="47">
-        <f>G18/13</f>
+      <c r="G19" s="35">
+        <f t="shared" si="0"/>
         <v>2.3076923076923075</v>
       </c>
-      <c r="H19" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="43">
+      <c r="H19" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="I19" s="29">
         <v>0.25</v>
       </c>
-      <c r="J19" s="43">
+      <c r="J19" s="29">
         <v>0.25</v>
       </c>
-      <c r="K19" s="43">
+      <c r="K19" s="29">
         <v>0.25</v>
       </c>
-      <c r="L19" s="44"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="45"/>
-      <c r="P19" s="45"/>
-      <c r="Q19" s="45"/>
-      <c r="R19" s="45"/>
-      <c r="S19" s="45"/>
-      <c r="T19" s="45"/>
-      <c r="U19" s="45"/>
-      <c r="V19" s="45"/>
-      <c r="W19" s="45"/>
-      <c r="X19" s="45"/>
-      <c r="Y19" s="45"/>
-      <c r="Z19" s="45"/>
-      <c r="AA19" s="45"/>
-      <c r="AB19" s="45"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="33"/>
+      <c r="S19" s="33"/>
+      <c r="T19" s="33"/>
+      <c r="U19" s="33"/>
+      <c r="V19" s="33"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="33"/>
+      <c r="Y19" s="33"/>
+      <c r="Z19" s="33"/>
+      <c r="AA19" s="33"/>
+      <c r="AB19" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B12:B16"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B8:B11"/>
     <mergeCell ref="C1:K1"/>
+    <mergeCell ref="D2:H2"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="B4:B7"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D16">
-    <cfRule type="colorScale" priority="40">
+    <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$D$19/2"/>
@@ -1790,7 +1743,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="41">
+    <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="&quot;MAX($A$1:$C$10)/2&quot;"/>
@@ -1800,7 +1753,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="42">
+    <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1812,7 +1765,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E16">
-    <cfRule type="colorScale" priority="43">
+    <cfRule type="colorScale" priority="53">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$E$19/2"/>
@@ -1824,7 +1777,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F16">
-    <cfRule type="colorScale" priority="44">
+    <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$F$19/2"/>
@@ -1836,7 +1789,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G16">
-    <cfRule type="colorScale" priority="45">
+    <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$G$19/2"/>
@@ -1846,7 +1799,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="46">
+    <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1858,7 +1811,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I16">
-    <cfRule type="colorScale" priority="47">
+    <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$I$19/2"/>
@@ -1870,7 +1823,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J16">
-    <cfRule type="colorScale" priority="48">
+    <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$J$19/2"/>
@@ -1882,7 +1835,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K16">
-    <cfRule type="colorScale" priority="49">
+    <cfRule type="colorScale" priority="59">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$K$19/2"/>
@@ -1894,7 +1847,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="8" scale="88" orientation="landscape"/>
+  <pageSetup paperSize="8" scale="88" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/Heat map 5.xlsx
+++ b/data/Heat map 5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B2B48F-ED00-4AF9-A084-492253E38B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799B46F6-6019-4CA2-AA58-FC14851383F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9DC939E2-9D2B-49F9-96FE-7432C9E71486}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_Hlk200085589" localSheetId="0">'Reputation, Society'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$L$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$K$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>KPI by Nr.</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>Approved proposals with nutrition ad health components</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -598,20 +601,10 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -638,15 +631,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -660,9 +648,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -672,9 +657,6 @@
     </xf>
     <xf numFmtId="9" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1119,609 +1101,559 @@
     <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AB19"/>
+  <dimension ref="B1:X26"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="3.21875" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" style="21" customWidth="1"/>
-    <col min="4" max="5" width="9.77734375" style="44" customWidth="1"/>
-    <col min="6" max="6" width="9.77734375" style="45" customWidth="1"/>
-    <col min="7" max="11" width="9.77734375" style="18" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" style="2" customWidth="1"/>
-    <col min="13" max="14" width="8.21875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="3.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" style="14" customWidth="1"/>
+    <col min="4" max="5" width="9.77734375" style="35" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" style="36" customWidth="1"/>
+    <col min="7" max="11" width="9.77734375" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="15" thickBot="1">
+    <row r="1" spans="2:11" ht="15" thickBot="1">
       <c r="B1" s="1"/>
-      <c r="C1" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="62"/>
-    </row>
-    <row r="2" spans="2:14" s="7" customFormat="1" ht="25.95" customHeight="1" thickBot="1">
-      <c r="B2" s="4"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="63" t="s">
+      <c r="C1" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="53"/>
+    </row>
+    <row r="2" spans="2:11" s="3" customFormat="1" ht="25.95" customHeight="1" thickBot="1">
+      <c r="B2" s="2"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="66" t="s">
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="66"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="2:14" s="17" customFormat="1" ht="132" customHeight="1" thickBot="1">
+      <c r="J2" s="57"/>
+      <c r="K2" s="58"/>
+    </row>
+    <row r="3" spans="2:11" s="11" customFormat="1" ht="132" customHeight="1" thickBot="1">
       <c r="B3" s="1"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="15"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-    </row>
-    <row r="4" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B4" s="56" t="s">
+    </row>
+    <row r="4" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B4" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="27">
         <v>17</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="E4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="37">
+      <c r="F4" s="28">
         <v>1</v>
       </c>
-      <c r="G4" s="37">
-        <v>0</v>
-      </c>
-      <c r="H4" s="38"/>
-      <c r="I4" s="47">
-        <v>0</v>
-      </c>
-      <c r="J4" s="48">
-        <v>0</v>
-      </c>
-      <c r="K4" s="49">
-        <v>0</v>
-      </c>
-      <c r="L4" s="18"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-    </row>
-    <row r="5" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B5" s="57"/>
-      <c r="C5" s="23" t="s">
+      <c r="G4" s="28">
+        <v>0</v>
+      </c>
+      <c r="H4" s="29"/>
+      <c r="I4" s="38">
+        <v>0</v>
+      </c>
+      <c r="J4" s="39">
+        <v>0</v>
+      </c>
+      <c r="K4" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B5" s="48"/>
+      <c r="C5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="27">
         <v>23</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="37">
-        <v>0</v>
-      </c>
-      <c r="G5" s="37">
+      <c r="F5" s="28">
+        <v>0</v>
+      </c>
+      <c r="G5" s="28">
         <v>3</v>
       </c>
-      <c r="H5" s="38"/>
-      <c r="I5" s="50">
+      <c r="H5" s="29"/>
+      <c r="I5" s="41">
         <v>0.28999999999999998</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="42">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="40">
         <v>0.28999999999999998</v>
       </c>
-      <c r="L5" s="18"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-    </row>
-    <row r="6" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B6" s="57"/>
-      <c r="C6" s="23" t="s">
+    </row>
+    <row r="6" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B6" s="48"/>
+      <c r="C6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="27">
         <v>19</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="37">
-        <v>0</v>
-      </c>
-      <c r="G6" s="37">
+      <c r="F6" s="28">
+        <v>0</v>
+      </c>
+      <c r="G6" s="28">
         <v>1</v>
       </c>
-      <c r="H6" s="38"/>
-      <c r="I6" s="50">
-        <v>0</v>
-      </c>
-      <c r="J6" s="51">
-        <v>0</v>
-      </c>
-      <c r="K6" s="52">
-        <v>0</v>
-      </c>
-      <c r="L6" s="18"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-    </row>
-    <row r="7" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B7" s="58"/>
-      <c r="C7" s="24" t="s">
+      <c r="H6" s="29"/>
+      <c r="I6" s="41">
+        <v>0</v>
+      </c>
+      <c r="J6" s="42">
+        <v>0</v>
+      </c>
+      <c r="K6" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B7" s="49"/>
+      <c r="C7" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="36">
-        <v>0</v>
-      </c>
-      <c r="E7" s="37">
+      <c r="D7" s="27">
+        <v>0</v>
+      </c>
+      <c r="E7" s="28">
         <v>14</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="28">
         <v>3</v>
       </c>
-      <c r="G7" s="37">
-        <v>0</v>
-      </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="53">
+      <c r="G7" s="28">
+        <v>0</v>
+      </c>
+      <c r="H7" s="29"/>
+      <c r="I7" s="44">
         <v>0.43</v>
       </c>
-      <c r="J7" s="54">
+      <c r="J7" s="45">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K7" s="55">
+      <c r="K7" s="46">
         <v>0.14000000000000001</v>
       </c>
-      <c r="L7" s="18"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-    </row>
-    <row r="8" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B8" s="56" t="s">
+    </row>
+    <row r="8" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B8" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="27">
         <v>18</v>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="28">
         <v>1</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="28">
         <v>3</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="28">
         <v>5</v>
       </c>
-      <c r="H8" s="38"/>
-      <c r="I8" s="47">
+      <c r="H8" s="29"/>
+      <c r="I8" s="38">
         <v>0.33</v>
       </c>
-      <c r="J8" s="48">
+      <c r="J8" s="39">
         <v>0.33</v>
       </c>
-      <c r="K8" s="49">
-        <v>0</v>
-      </c>
-      <c r="L8" s="18"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-    </row>
-    <row r="9" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B9" s="57"/>
-      <c r="C9" s="23" t="s">
+      <c r="K8" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B9" s="48"/>
+      <c r="C9" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="27">
         <v>43</v>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="28">
         <v>17</v>
       </c>
-      <c r="F9" s="37">
-        <v>0</v>
-      </c>
-      <c r="G9" s="37">
+      <c r="F9" s="28">
+        <v>0</v>
+      </c>
+      <c r="G9" s="28">
         <v>3</v>
       </c>
-      <c r="H9" s="38"/>
-      <c r="I9" s="50">
+      <c r="H9" s="29"/>
+      <c r="I9" s="41">
         <v>0.44</v>
       </c>
-      <c r="J9" s="51">
+      <c r="J9" s="42">
         <v>0.44</v>
       </c>
-      <c r="K9" s="55">
+      <c r="K9" s="46">
         <v>0.11</v>
       </c>
-      <c r="L9" s="18"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-    </row>
-    <row r="10" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B10" s="57"/>
-      <c r="C10" s="23" t="s">
+    </row>
+    <row r="10" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B10" s="48"/>
+      <c r="C10" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="36">
-        <v>0</v>
-      </c>
-      <c r="E10" s="37">
+      <c r="D10" s="27">
+        <v>0</v>
+      </c>
+      <c r="E10" s="28">
         <v>3</v>
       </c>
-      <c r="F10" s="37">
-        <v>0</v>
-      </c>
-      <c r="G10" s="37">
-        <v>0</v>
-      </c>
-      <c r="H10" s="38"/>
-      <c r="I10" s="50">
+      <c r="F10" s="28">
+        <v>0</v>
+      </c>
+      <c r="G10" s="28">
+        <v>0</v>
+      </c>
+      <c r="H10" s="29"/>
+      <c r="I10" s="41">
         <v>0.56999999999999995</v>
       </c>
-      <c r="J10" s="51">
+      <c r="J10" s="42">
         <v>0.71</v>
       </c>
-      <c r="K10" s="52">
-        <v>0</v>
-      </c>
-      <c r="L10" s="18"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-    </row>
-    <row r="11" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B11" s="58"/>
-      <c r="C11" s="24" t="s">
+      <c r="K10" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B11" s="49"/>
+      <c r="C11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="36">
-        <v>0</v>
-      </c>
-      <c r="E11" s="37">
-        <v>0</v>
-      </c>
-      <c r="F11" s="37">
-        <v>0</v>
-      </c>
-      <c r="G11" s="37">
-        <v>0</v>
-      </c>
-      <c r="H11" s="38"/>
-      <c r="I11" s="53">
-        <v>0</v>
-      </c>
-      <c r="J11" s="54">
-        <v>0</v>
-      </c>
-      <c r="K11" s="55">
-        <v>0</v>
-      </c>
-      <c r="L11" s="18"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-    </row>
-    <row r="12" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B12" s="56" t="s">
+      <c r="D11" s="27">
+        <v>0</v>
+      </c>
+      <c r="E11" s="28">
+        <v>0</v>
+      </c>
+      <c r="F11" s="28">
+        <v>0</v>
+      </c>
+      <c r="G11" s="28">
+        <v>0</v>
+      </c>
+      <c r="H11" s="29"/>
+      <c r="I11" s="44">
+        <v>0</v>
+      </c>
+      <c r="J11" s="45">
+        <v>0</v>
+      </c>
+      <c r="K11" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B12" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="27">
         <v>7</v>
       </c>
-      <c r="E12" s="39">
-        <v>0</v>
-      </c>
-      <c r="F12" s="39">
-        <v>0</v>
-      </c>
-      <c r="G12" s="37">
-        <v>0</v>
-      </c>
-      <c r="H12" s="38"/>
-      <c r="I12" s="47">
-        <v>0</v>
-      </c>
-      <c r="J12" s="48">
-        <v>0</v>
-      </c>
-      <c r="K12" s="49">
-        <v>0</v>
-      </c>
-      <c r="L12" s="18"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-    </row>
-    <row r="13" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B13" s="57"/>
-      <c r="C13" s="23" t="s">
+      <c r="E12" s="30">
+        <v>0</v>
+      </c>
+      <c r="F12" s="30">
+        <v>0</v>
+      </c>
+      <c r="G12" s="28">
+        <v>0</v>
+      </c>
+      <c r="H12" s="29"/>
+      <c r="I12" s="38">
+        <v>0</v>
+      </c>
+      <c r="J12" s="39">
+        <v>0</v>
+      </c>
+      <c r="K12" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B13" s="48"/>
+      <c r="C13" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="36">
-        <v>0</v>
-      </c>
-      <c r="E13" s="39">
-        <v>0</v>
-      </c>
-      <c r="F13" s="39">
-        <v>0</v>
-      </c>
-      <c r="G13" s="37">
+      <c r="D13" s="27">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30">
+        <v>0</v>
+      </c>
+      <c r="F13" s="30">
+        <v>0</v>
+      </c>
+      <c r="G13" s="28">
         <v>3</v>
       </c>
-      <c r="H13" s="38"/>
-      <c r="I13" s="50">
-        <v>0</v>
-      </c>
-      <c r="J13" s="51">
-        <v>0</v>
-      </c>
-      <c r="K13" s="52">
-        <v>0</v>
-      </c>
-      <c r="L13" s="18"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-    </row>
-    <row r="14" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B14" s="57"/>
-      <c r="C14" s="23" t="s">
+      <c r="H13" s="29"/>
+      <c r="I13" s="41">
+        <v>0</v>
+      </c>
+      <c r="J13" s="42">
+        <v>0</v>
+      </c>
+      <c r="K13" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B14" s="48"/>
+      <c r="C14" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="27">
         <v>6</v>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="30">
         <v>3</v>
       </c>
-      <c r="F14" s="39">
-        <v>0</v>
-      </c>
-      <c r="G14" s="37">
+      <c r="F14" s="30">
+        <v>0</v>
+      </c>
+      <c r="G14" s="28">
         <v>3</v>
       </c>
-      <c r="H14" s="38"/>
-      <c r="I14" s="50">
-        <v>0</v>
-      </c>
-      <c r="J14" s="51">
-        <v>0</v>
-      </c>
-      <c r="K14" s="52">
-        <v>0</v>
-      </c>
-      <c r="L14" s="18"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-    </row>
-    <row r="15" spans="2:14" s="20" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B15" s="57"/>
-      <c r="C15" s="23" t="s">
+      <c r="H14" s="29"/>
+      <c r="I14" s="41">
+        <v>0</v>
+      </c>
+      <c r="J14" s="42">
+        <v>0</v>
+      </c>
+      <c r="K14" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B15" s="48"/>
+      <c r="C15" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="27">
         <v>7</v>
       </c>
-      <c r="E15" s="39">
-        <v>0</v>
-      </c>
-      <c r="F15" s="39">
-        <v>0</v>
-      </c>
-      <c r="G15" s="37">
-        <v>0</v>
-      </c>
-      <c r="H15" s="38"/>
-      <c r="I15" s="50">
-        <v>0</v>
-      </c>
-      <c r="J15" s="51">
-        <v>0</v>
-      </c>
-      <c r="K15" s="52">
-        <v>0</v>
-      </c>
-      <c r="L15" s="18"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-    </row>
-    <row r="16" spans="2:14" s="20" customFormat="1" ht="15.45" customHeight="1" thickBot="1">
-      <c r="B16" s="58"/>
-      <c r="C16" s="24" t="s">
+      <c r="E15" s="30">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30">
+        <v>0</v>
+      </c>
+      <c r="G15" s="28">
+        <v>0</v>
+      </c>
+      <c r="H15" s="29"/>
+      <c r="I15" s="41">
+        <v>0</v>
+      </c>
+      <c r="J15" s="42">
+        <v>0</v>
+      </c>
+      <c r="K15" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" s="13" customFormat="1" ht="15.45" customHeight="1" thickBot="1">
+      <c r="B16" s="49"/>
+      <c r="C16" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="40">
-        <v>0</v>
-      </c>
-      <c r="E16" s="41">
-        <v>0</v>
-      </c>
-      <c r="F16" s="41">
+      <c r="D16" s="31">
+        <v>0</v>
+      </c>
+      <c r="E16" s="32">
+        <v>0</v>
+      </c>
+      <c r="F16" s="32">
         <v>1</v>
       </c>
-      <c r="G16" s="42">
-        <v>0</v>
-      </c>
-      <c r="H16" s="43"/>
-      <c r="I16" s="53">
+      <c r="G16" s="33">
+        <v>0</v>
+      </c>
+      <c r="H16" s="34"/>
+      <c r="I16" s="44">
         <v>1</v>
       </c>
-      <c r="J16" s="54">
-        <v>0</v>
-      </c>
-      <c r="K16" s="55">
-        <v>0</v>
-      </c>
-      <c r="L16" s="18"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-    </row>
-    <row r="17" spans="2:28" s="31" customFormat="1" ht="12">
-      <c r="B17" s="26"/>
-      <c r="C17" s="27" t="s">
+      <c r="J16" s="45">
+        <v>0</v>
+      </c>
+      <c r="K16" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" s="22" customFormat="1" ht="12">
+      <c r="B17" s="18"/>
+      <c r="C17" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="20">
         <f>SUM(D4:D16)</f>
         <v>140</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="20">
         <f>SUM(E4:E16)</f>
         <v>38</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="20">
         <f>SUM(F4:F16)</f>
         <v>8</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="20">
         <f>SUM(G4:G16)</f>
         <v>18</v>
       </c>
-      <c r="H17" s="28">
+      <c r="H17" s="20">
         <v>30</v>
       </c>
-      <c r="I17" s="29" t="s">
+      <c r="I17" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="J17" s="29" t="s">
+      <c r="J17" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K17" s="29" t="s">
+      <c r="K17" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="L17" s="30"/>
-    </row>
-    <row r="18" spans="2:28" s="34" customFormat="1">
-      <c r="B18" s="32"/>
-      <c r="C18" s="27" t="s">
+    </row>
+    <row r="18" spans="2:24" s="25" customFormat="1">
+      <c r="B18" s="23"/>
+      <c r="C18" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="20">
         <v>30</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="19">
         <v>25</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="20">
         <v>30</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="20">
         <v>30</v>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="19">
         <v>15</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="21">
         <v>0.25</v>
       </c>
-      <c r="J18" s="29">
+      <c r="J18" s="21">
         <v>0.25</v>
       </c>
-      <c r="K18" s="29">
+      <c r="K18" s="21">
         <v>0.25</v>
       </c>
-      <c r="L18" s="25"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-    </row>
-    <row r="19" spans="2:28" s="34" customFormat="1">
-      <c r="B19" s="32"/>
-      <c r="C19" s="27" t="s">
+    </row>
+    <row r="19" spans="2:24" s="25" customFormat="1">
+      <c r="B19" s="23"/>
+      <c r="C19" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="26">
         <f>D18/13</f>
         <v>2.3076923076923075</v>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="26">
         <f t="shared" ref="E19:G19" si="0">E18/13</f>
         <v>1.9230769230769231</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="26">
         <f t="shared" si="0"/>
         <v>2.3076923076923075</v>
       </c>
-      <c r="G19" s="35">
+      <c r="G19" s="26">
         <f t="shared" si="0"/>
         <v>2.3076923076923075</v>
       </c>
-      <c r="H19" s="35" t="s">
+      <c r="H19" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="I19" s="29">
+      <c r="I19" s="21">
         <v>0.25</v>
       </c>
-      <c r="J19" s="29">
+      <c r="J19" s="21">
         <v>0.25</v>
       </c>
-      <c r="K19" s="29">
+      <c r="K19" s="21">
         <v>0.25</v>
       </c>
-      <c r="L19" s="25"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
-      <c r="T19" s="33"/>
-      <c r="U19" s="33"/>
-      <c r="V19" s="33"/>
-      <c r="W19" s="33"/>
-      <c r="X19" s="33"/>
-      <c r="Y19" s="33"/>
-      <c r="Z19" s="33"/>
-      <c r="AA19" s="33"/>
-      <c r="AB19" s="33"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="24"/>
+      <c r="U19" s="24"/>
+      <c r="V19" s="24"/>
+      <c r="W19" s="24"/>
+      <c r="X19" s="24"/>
+    </row>
+    <row r="26" spans="2:24">
+      <c r="F26" s="36" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/data/Heat map 5.xlsx
+++ b/data/Heat map 5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799B46F6-6019-4CA2-AA58-FC14851383F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAC98E1-615E-400E-A57E-8C9C79BC41AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9DC939E2-9D2B-49F9-96FE-7432C9E71486}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9DC939E2-9D2B-49F9-96FE-7432C9E71486}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
@@ -51,9 +51,6 @@
     <t>Society Impact &amp; Inclusion</t>
   </si>
   <si>
-    <t>GI</t>
-  </si>
-  <si>
     <t>Biotech</t>
   </si>
   <si>
@@ -69,9 +66,6 @@
     <t>Seed System</t>
   </si>
   <si>
-    <t>RAFS</t>
-  </si>
-  <si>
     <t>Plant Health</t>
   </si>
   <si>
@@ -81,9 +75,6 @@
     <t>Mechanization</t>
   </si>
   <si>
-    <t>ST</t>
-  </si>
-  <si>
     <t>2025 Actual Values</t>
   </si>
   <si>
@@ -136,6 +127,15 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Genetic Innovation</t>
+  </si>
+  <si>
+    <t>Resilient Agrifood Systems</t>
+  </si>
+  <si>
+    <t>Systems Transformation</t>
   </si>
 </sst>
 </file>
@@ -1145,42 +1145,42 @@
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="I3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="J3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="K3" s="10" t="s">
         <v>27</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
       <c r="B4" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>3</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>4</v>
       </c>
       <c r="D4" s="27">
         <v>17</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="28">
         <v>1</v>
@@ -1202,13 +1202,13 @@
     <row r="5" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B5" s="48"/>
       <c r="C5" s="16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="27">
         <v>23</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="28">
         <v>0</v>
@@ -1230,13 +1230,13 @@
     <row r="6" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B6" s="48"/>
       <c r="C6" s="16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" s="27">
         <v>19</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="28">
         <v>0</v>
@@ -1258,7 +1258,7 @@
     <row r="7" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
       <c r="B7" s="49"/>
       <c r="C7" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" s="27">
         <v>0</v>
@@ -1285,10 +1285,10 @@
     </row>
     <row r="8" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B8" s="47" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" s="27">
         <v>18</v>
@@ -1316,7 +1316,7 @@
     <row r="9" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
       <c r="B9" s="48"/>
       <c r="C9" s="16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D9" s="27">
         <v>43</v>
@@ -1344,7 +1344,7 @@
     <row r="10" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B10" s="48"/>
       <c r="C10" s="16" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D10" s="27">
         <v>0</v>
@@ -1372,7 +1372,7 @@
     <row r="11" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
       <c r="B11" s="49"/>
       <c r="C11" s="17" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="27">
         <v>0</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="12" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B12" s="47" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D12" s="27">
         <v>7</v>
@@ -1430,7 +1430,7 @@
     <row r="13" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B13" s="48"/>
       <c r="C13" s="16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D13" s="27">
         <v>0</v>
@@ -1458,7 +1458,7 @@
     <row r="14" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B14" s="48"/>
       <c r="C14" s="16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D14" s="27">
         <v>6</v>
@@ -1486,7 +1486,7 @@
     <row r="15" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
       <c r="B15" s="48"/>
       <c r="C15" s="16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D15" s="27">
         <v>7</v>
@@ -1514,7 +1514,7 @@
     <row r="16" spans="2:11" s="13" customFormat="1" ht="15.45" customHeight="1" thickBot="1">
       <c r="B16" s="49"/>
       <c r="C16" s="17" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D16" s="31">
         <v>0</v>
@@ -1542,7 +1542,7 @@
     <row r="17" spans="2:24" s="22" customFormat="1" ht="12">
       <c r="B17" s="18"/>
       <c r="C17" s="19" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D17" s="20">
         <f>SUM(D4:D16)</f>
@@ -1564,19 +1564,19 @@
         <v>30</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="2:24" s="25" customFormat="1">
       <c r="B18" s="23"/>
       <c r="C18" s="19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D18" s="20">
         <v>30</v>
@@ -1606,7 +1606,7 @@
     <row r="19" spans="2:24" s="25" customFormat="1">
       <c r="B19" s="23"/>
       <c r="C19" s="19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D19" s="26">
         <f>D18/13</f>
@@ -1625,7 +1625,7 @@
         <v>2.3076923076923075</v>
       </c>
       <c r="H19" s="26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I19" s="21">
         <v>0.25</v>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="26" spans="2:24">
       <c r="F26" s="36" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/data/Heat map 5.xlsx
+++ b/data/Heat map 5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAC98E1-615E-400E-A57E-8C9C79BC41AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036980D9-2D3B-42ED-B304-E3691613A516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9DC939E2-9D2B-49F9-96FE-7432C9E71486}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
   <si>
     <t>KPI by Nr.</t>
   </si>
@@ -147,7 +147,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -601,7 +601,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -684,9 +684,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1102,46 +1099,46 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:X26"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="3.21875" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.21875" style="14" customWidth="1"/>
-    <col min="4" max="5" width="9.77734375" style="35" customWidth="1"/>
-    <col min="6" max="6" width="9.77734375" style="36" customWidth="1"/>
+    <col min="4" max="5" width="9.77734375" style="34" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" style="35" customWidth="1"/>
     <col min="7" max="11" width="9.77734375" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15" thickBot="1">
+    <row r="1" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
-      <c r="C1" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="53"/>
-    </row>
-    <row r="2" spans="2:11" s="3" customFormat="1" ht="25.95" customHeight="1" thickBot="1">
+      <c r="C1" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="52"/>
+    </row>
+    <row r="2" spans="2:11" s="3" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="54" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="57" t="s">
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
-    </row>
-    <row r="3" spans="2:11" s="11" customFormat="1" ht="132" customHeight="1" thickBot="1">
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
+    </row>
+    <row r="3" spans="2:11" s="11" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="s">
@@ -1169,8 +1166,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B4" s="47" t="s">
+    <row r="4" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="46" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="15" t="s">
@@ -1188,19 +1185,21 @@
       <c r="G4" s="28">
         <v>0</v>
       </c>
-      <c r="H4" s="29"/>
-      <c r="I4" s="38">
-        <v>0</v>
-      </c>
-      <c r="J4" s="39">
-        <v>0</v>
-      </c>
-      <c r="K4" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B5" s="48"/>
+      <c r="H4" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="37">
+        <v>0</v>
+      </c>
+      <c r="J4" s="38">
+        <v>0</v>
+      </c>
+      <c r="K4" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="47"/>
       <c r="C5" s="16" t="s">
         <v>5</v>
       </c>
@@ -1216,19 +1215,21 @@
       <c r="G5" s="28">
         <v>3</v>
       </c>
-      <c r="H5" s="29"/>
-      <c r="I5" s="41">
+      <c r="H5" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="40">
         <v>0.28999999999999998</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="41">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="39">
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="6" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B6" s="48"/>
+    <row r="6" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="47"/>
       <c r="C6" s="16" t="s">
         <v>6</v>
       </c>
@@ -1244,19 +1245,21 @@
       <c r="G6" s="28">
         <v>1</v>
       </c>
-      <c r="H6" s="29"/>
-      <c r="I6" s="41">
-        <v>0</v>
-      </c>
-      <c r="J6" s="42">
-        <v>0</v>
-      </c>
-      <c r="K6" s="43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B7" s="49"/>
+      <c r="H6" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="40">
+        <v>0</v>
+      </c>
+      <c r="J6" s="41">
+        <v>0</v>
+      </c>
+      <c r="K6" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="48"/>
       <c r="C7" s="17" t="s">
         <v>7</v>
       </c>
@@ -1272,19 +1275,21 @@
       <c r="G7" s="28">
         <v>0</v>
       </c>
-      <c r="H7" s="29"/>
-      <c r="I7" s="44">
+      <c r="H7" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" s="43">
         <v>0.43</v>
       </c>
-      <c r="J7" s="45">
+      <c r="J7" s="44">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K7" s="46">
+      <c r="K7" s="45">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="8" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B8" s="47" t="s">
+    <row r="8" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="46" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="15" t="s">
@@ -1302,19 +1307,21 @@
       <c r="G8" s="28">
         <v>5</v>
       </c>
-      <c r="H8" s="29"/>
-      <c r="I8" s="38">
+      <c r="H8" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="37">
         <v>0.33</v>
       </c>
-      <c r="J8" s="39">
+      <c r="J8" s="38">
         <v>0.33</v>
       </c>
-      <c r="K8" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B9" s="48"/>
+      <c r="K8" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="47"/>
       <c r="C9" s="16" t="s">
         <v>9</v>
       </c>
@@ -1330,19 +1337,21 @@
       <c r="G9" s="28">
         <v>3</v>
       </c>
-      <c r="H9" s="29"/>
-      <c r="I9" s="41">
+      <c r="H9" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="40">
         <v>0.44</v>
       </c>
-      <c r="J9" s="42">
+      <c r="J9" s="41">
         <v>0.44</v>
       </c>
-      <c r="K9" s="46">
+      <c r="K9" s="45">
         <v>0.11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B10" s="48"/>
+    <row r="10" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="47"/>
       <c r="C10" s="16" t="s">
         <v>14</v>
       </c>
@@ -1358,19 +1367,21 @@
       <c r="G10" s="28">
         <v>0</v>
       </c>
-      <c r="H10" s="29"/>
-      <c r="I10" s="41">
+      <c r="H10" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="40">
         <v>0.56999999999999995</v>
       </c>
-      <c r="J10" s="42">
+      <c r="J10" s="41">
         <v>0.71</v>
       </c>
-      <c r="K10" s="43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B11" s="49"/>
+      <c r="K10" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="48"/>
       <c r="C11" s="17" t="s">
         <v>10</v>
       </c>
@@ -1386,19 +1397,21 @@
       <c r="G11" s="28">
         <v>0</v>
       </c>
-      <c r="H11" s="29"/>
-      <c r="I11" s="44">
-        <v>0</v>
-      </c>
-      <c r="J11" s="45">
-        <v>0</v>
-      </c>
-      <c r="K11" s="46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B12" s="47" t="s">
+      <c r="H11" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11" s="43">
+        <v>0</v>
+      </c>
+      <c r="J11" s="44">
+        <v>0</v>
+      </c>
+      <c r="K11" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="46" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="15" t="s">
@@ -1416,19 +1429,21 @@
       <c r="G12" s="28">
         <v>0</v>
       </c>
-      <c r="H12" s="29"/>
-      <c r="I12" s="38">
-        <v>0</v>
-      </c>
-      <c r="J12" s="39">
-        <v>0</v>
-      </c>
-      <c r="K12" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B13" s="48"/>
+      <c r="H12" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="37">
+        <v>0</v>
+      </c>
+      <c r="J12" s="38">
+        <v>0</v>
+      </c>
+      <c r="K12" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="47"/>
       <c r="C13" s="16" t="s">
         <v>16</v>
       </c>
@@ -1444,19 +1459,21 @@
       <c r="G13" s="28">
         <v>3</v>
       </c>
-      <c r="H13" s="29"/>
-      <c r="I13" s="41">
-        <v>0</v>
-      </c>
-      <c r="J13" s="42">
-        <v>0</v>
-      </c>
-      <c r="K13" s="43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B14" s="48"/>
+      <c r="H13" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I13" s="40">
+        <v>0</v>
+      </c>
+      <c r="J13" s="41">
+        <v>0</v>
+      </c>
+      <c r="K13" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="47"/>
       <c r="C14" s="16" t="s">
         <v>17</v>
       </c>
@@ -1472,19 +1489,21 @@
       <c r="G14" s="28">
         <v>3</v>
       </c>
-      <c r="H14" s="29"/>
-      <c r="I14" s="41">
-        <v>0</v>
-      </c>
-      <c r="J14" s="42">
-        <v>0</v>
-      </c>
-      <c r="K14" s="43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B15" s="48"/>
+      <c r="H14" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="40">
+        <v>0</v>
+      </c>
+      <c r="J14" s="41">
+        <v>0</v>
+      </c>
+      <c r="K14" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="47"/>
       <c r="C15" s="16" t="s">
         <v>18</v>
       </c>
@@ -1500,19 +1519,21 @@
       <c r="G15" s="28">
         <v>0</v>
       </c>
-      <c r="H15" s="29"/>
-      <c r="I15" s="41">
-        <v>0</v>
-      </c>
-      <c r="J15" s="42">
-        <v>0</v>
-      </c>
-      <c r="K15" s="43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" s="13" customFormat="1" ht="15.45" customHeight="1" thickBot="1">
-      <c r="B16" s="49"/>
+      <c r="H15" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" s="40">
+        <v>0</v>
+      </c>
+      <c r="J15" s="41">
+        <v>0</v>
+      </c>
+      <c r="K15" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" s="13" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="48"/>
       <c r="C16" s="17" t="s">
         <v>19</v>
       </c>
@@ -1528,18 +1549,20 @@
       <c r="G16" s="33">
         <v>0</v>
       </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="44">
+      <c r="H16" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I16" s="43">
         <v>1</v>
       </c>
-      <c r="J16" s="45">
-        <v>0</v>
-      </c>
-      <c r="K16" s="46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:24" s="22" customFormat="1" ht="12">
+      <c r="J16" s="44">
+        <v>0</v>
+      </c>
+      <c r="K16" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" s="22" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B17" s="18"/>
       <c r="C17" s="19" t="s">
         <v>11</v>
@@ -1573,7 +1596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="2:24" s="25" customFormat="1">
+    <row r="18" spans="2:24" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="23"/>
       <c r="C18" s="19" t="s">
         <v>12</v>
@@ -1603,7 +1626,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="19" spans="2:24" s="25" customFormat="1">
+    <row r="19" spans="2:24" s="25" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B19" s="23"/>
       <c r="C19" s="19" t="s">
         <v>13</v>
@@ -1650,8 +1673,8 @@
       <c r="W19" s="24"/>
       <c r="X19" s="24"/>
     </row>
-    <row r="26" spans="2:24">
-      <c r="F26" s="36" t="s">
+    <row r="26" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="F26" s="35" t="s">
         <v>28</v>
       </c>
     </row>

--- a/data/Heat map 5.xlsx
+++ b/data/Heat map 5.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036980D9-2D3B-42ED-B304-E3691613A516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CB64B3-BFDF-4C97-81C2-632990975411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9DC939E2-9D2B-49F9-96FE-7432C9E71486}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9DC939E2-9D2B-49F9-96FE-7432C9E71486}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_Hlk200085589" localSheetId="0">'Reputation, Society'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$K$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$K$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,10 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
-  <si>
-    <t>KPI by Nr.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
   <si>
     <t>Recognition and Reputation</t>
   </si>
@@ -238,7 +235,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -265,17 +262,19 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
@@ -283,49 +282,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -590,6 +546,104 @@
         <color theme="1"/>
       </right>
       <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -601,7 +655,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -610,27 +664,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -639,16 +672,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -659,31 +691,30 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -692,71 +723,83 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1098,601 +1141,589 @@
     <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:X26"/>
+  <dimension ref="B1:X25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.21875" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" style="14" customWidth="1"/>
-    <col min="4" max="5" width="9.77734375" style="34" customWidth="1"/>
-    <col min="6" max="6" width="9.77734375" style="35" customWidth="1"/>
-    <col min="7" max="11" width="9.77734375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="4.77734375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" style="7" customWidth="1"/>
+    <col min="4" max="5" width="9.77734375" style="25" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" style="26" customWidth="1"/>
+    <col min="7" max="11" width="9.77734375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="1"/>
-      <c r="C1" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
+    <row r="1" spans="2:11" s="3" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="2"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
       <c r="H1" s="50"/>
-      <c r="I1" s="51"/>
+      <c r="I1" s="51" t="s">
+        <v>1</v>
+      </c>
       <c r="J1" s="51"/>
       <c r="K1" s="52"/>
     </row>
-    <row r="2" spans="2:11" s="3" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="2"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="53" t="s">
+    <row r="2" spans="2:11" s="4" customFormat="1" ht="106.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="47" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="18">
+        <v>17</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="19">
         <v>1</v>
       </c>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="56" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2" s="56"/>
-      <c r="K2" s="57"/>
+      <c r="G3" s="19">
+        <v>0</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="28">
+        <v>0</v>
+      </c>
+      <c r="J3" s="29">
+        <v>0</v>
+      </c>
+      <c r="K3" s="30">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="2:11" s="11" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="1"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="6" t="s">
+    <row r="4" spans="2:11" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="38"/>
+      <c r="C4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="18">
         <v>23</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="E4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>0</v>
+      </c>
+      <c r="G4" s="19">
+        <v>3</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="31">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J4" s="32">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K4" s="30">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="38"/>
+      <c r="C5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="18">
+        <v>19</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="19">
+        <v>0</v>
+      </c>
+      <c r="G5" s="19">
+        <v>1</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="31">
+        <v>0</v>
+      </c>
+      <c r="J5" s="32">
+        <v>0</v>
+      </c>
+      <c r="K5" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="39"/>
+      <c r="C6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="18">
+        <v>0</v>
+      </c>
+      <c r="E6" s="19">
+        <v>14</v>
+      </c>
+      <c r="F6" s="19">
+        <v>3</v>
+      </c>
+      <c r="G6" s="19">
+        <v>0</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="34">
+        <v>0.43</v>
+      </c>
+      <c r="J6" s="35">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="K6" s="36">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="18">
+        <v>18</v>
+      </c>
+      <c r="E7" s="19">
+        <v>1</v>
+      </c>
+      <c r="F7" s="19">
+        <v>3</v>
+      </c>
+      <c r="G7" s="19">
+        <v>5</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="28">
+        <v>0.33</v>
+      </c>
+      <c r="J7" s="29">
+        <v>0.33</v>
+      </c>
+      <c r="K7" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="38"/>
+      <c r="C8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="18">
+        <v>43</v>
+      </c>
+      <c r="E8" s="19">
+        <v>17</v>
+      </c>
+      <c r="F8" s="19">
+        <v>0</v>
+      </c>
+      <c r="G8" s="19">
+        <v>3</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="31">
+        <v>0.44</v>
+      </c>
+      <c r="J8" s="32">
+        <v>0.44</v>
+      </c>
+      <c r="K8" s="36">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="38"/>
+      <c r="C9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="18">
+        <v>0</v>
+      </c>
+      <c r="E9" s="19">
+        <v>3</v>
+      </c>
+      <c r="F9" s="19">
+        <v>0</v>
+      </c>
+      <c r="G9" s="19">
+        <v>0</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="31">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J9" s="32">
+        <v>0.71</v>
+      </c>
+      <c r="K9" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="39"/>
+      <c r="C10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="18">
+        <v>0</v>
+      </c>
+      <c r="E10" s="19">
+        <v>0</v>
+      </c>
+      <c r="F10" s="19">
+        <v>0</v>
+      </c>
+      <c r="G10" s="19">
+        <v>0</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="34">
+        <v>0</v>
+      </c>
+      <c r="J10" s="35">
+        <v>0</v>
+      </c>
+      <c r="K10" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="18">
+        <v>7</v>
+      </c>
+      <c r="E11" s="21">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21">
+        <v>0</v>
+      </c>
+      <c r="G11" s="19">
+        <v>0</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="28">
+        <v>0</v>
+      </c>
+      <c r="J11" s="29">
+        <v>0</v>
+      </c>
+      <c r="K11" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="38"/>
+      <c r="C12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="18">
+        <v>0</v>
+      </c>
+      <c r="E12" s="21">
+        <v>0</v>
+      </c>
+      <c r="F12" s="21">
+        <v>0</v>
+      </c>
+      <c r="G12" s="19">
+        <v>3</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="31">
+        <v>0</v>
+      </c>
+      <c r="J12" s="32">
+        <v>0</v>
+      </c>
+      <c r="K12" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="38"/>
+      <c r="C13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="18">
+        <v>6</v>
+      </c>
+      <c r="E13" s="21">
+        <v>3</v>
+      </c>
+      <c r="F13" s="21">
+        <v>0</v>
+      </c>
+      <c r="G13" s="19">
+        <v>3</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="31">
+        <v>0</v>
+      </c>
+      <c r="J13" s="32">
+        <v>0</v>
+      </c>
+      <c r="K13" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="38"/>
+      <c r="C14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="18">
+        <v>7</v>
+      </c>
+      <c r="E14" s="21">
+        <v>0</v>
+      </c>
+      <c r="F14" s="21">
+        <v>0</v>
+      </c>
+      <c r="G14" s="19">
+        <v>0</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="31">
+        <v>0</v>
+      </c>
+      <c r="J14" s="32">
+        <v>0</v>
+      </c>
+      <c r="K14" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" s="6" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="39"/>
+      <c r="C15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="22">
+        <v>0</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>1</v>
+      </c>
+      <c r="G15" s="24">
+        <v>0</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="34">
+        <v>1</v>
+      </c>
+      <c r="J15" s="35">
+        <v>0</v>
+      </c>
+      <c r="K15" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" s="14" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="12">
+        <f>SUM(D3:D15)</f>
+        <v>140</v>
+      </c>
+      <c r="E16" s="12">
+        <f>SUM(E3:E15)</f>
+        <v>38</v>
+      </c>
+      <c r="F16" s="12">
+        <f>SUM(F3:F15)</f>
+        <v>8</v>
+      </c>
+      <c r="G16" s="12">
+        <f>SUM(G3:G15)</f>
+        <v>18</v>
+      </c>
+      <c r="H16" s="12">
+        <v>30</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="40"/>
+      <c r="D17" s="12">
+        <v>30</v>
+      </c>
+      <c r="E17" s="11">
         <v>25</v>
       </c>
-      <c r="J3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>27</v>
+      <c r="F17" s="12">
+        <v>30</v>
+      </c>
+      <c r="G17" s="12">
+        <v>30</v>
+      </c>
+      <c r="H17" s="11">
+        <v>15</v>
+      </c>
+      <c r="I17" s="13">
+        <v>0.25</v>
+      </c>
+      <c r="J17" s="13">
+        <v>0.25</v>
+      </c>
+      <c r="K17" s="13">
+        <v>0.25</v>
       </c>
     </row>
-    <row r="4" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="27">
-        <v>17</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="28">
-        <v>1</v>
-      </c>
-      <c r="G4" s="28">
-        <v>0</v>
-      </c>
-      <c r="H4" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" s="37">
-        <v>0</v>
-      </c>
-      <c r="J4" s="38">
-        <v>0</v>
-      </c>
-      <c r="K4" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="47"/>
-      <c r="C5" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="27">
-        <v>23</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="28">
-        <v>0</v>
-      </c>
-      <c r="G5" s="28">
-        <v>3</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5" s="40">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="J5" s="41">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K5" s="39">
-        <v>0.28999999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="47"/>
-      <c r="C6" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="27">
-        <v>19</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="28">
-        <v>0</v>
-      </c>
-      <c r="G6" s="28">
-        <v>1</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I6" s="40">
-        <v>0</v>
-      </c>
-      <c r="J6" s="41">
-        <v>0</v>
-      </c>
-      <c r="K6" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="48"/>
-      <c r="C7" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="27">
-        <v>0</v>
-      </c>
-      <c r="E7" s="28">
-        <v>14</v>
-      </c>
-      <c r="F7" s="28">
-        <v>3</v>
-      </c>
-      <c r="G7" s="28">
-        <v>0</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I7" s="43">
-        <v>0.43</v>
-      </c>
-      <c r="J7" s="44">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="K7" s="45">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="27">
-        <v>18</v>
-      </c>
-      <c r="E8" s="28">
-        <v>1</v>
-      </c>
-      <c r="F8" s="28">
-        <v>3</v>
-      </c>
-      <c r="G8" s="28">
-        <v>5</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="37">
-        <v>0.33</v>
-      </c>
-      <c r="J8" s="38">
-        <v>0.33</v>
-      </c>
-      <c r="K8" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="47"/>
-      <c r="C9" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="27">
-        <v>43</v>
-      </c>
-      <c r="E9" s="28">
-        <v>17</v>
-      </c>
-      <c r="F9" s="28">
-        <v>0</v>
-      </c>
-      <c r="G9" s="28">
-        <v>3</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="40">
-        <v>0.44</v>
-      </c>
-      <c r="J9" s="41">
-        <v>0.44</v>
-      </c>
-      <c r="K9" s="45">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
-      <c r="C10" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="27">
-        <v>0</v>
-      </c>
-      <c r="E10" s="28">
-        <v>3</v>
-      </c>
-      <c r="F10" s="28">
-        <v>0</v>
-      </c>
-      <c r="G10" s="28">
-        <v>0</v>
-      </c>
-      <c r="H10" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="40">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="J10" s="41">
-        <v>0.71</v>
-      </c>
-      <c r="K10" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="48"/>
-      <c r="C11" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="27">
-        <v>0</v>
-      </c>
-      <c r="E11" s="28">
-        <v>0</v>
-      </c>
-      <c r="F11" s="28">
-        <v>0</v>
-      </c>
-      <c r="G11" s="28">
-        <v>0</v>
-      </c>
-      <c r="H11" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I11" s="43">
-        <v>0</v>
-      </c>
-      <c r="J11" s="44">
-        <v>0</v>
-      </c>
-      <c r="K11" s="45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="27">
-        <v>7</v>
-      </c>
-      <c r="E12" s="30">
-        <v>0</v>
-      </c>
-      <c r="F12" s="30">
-        <v>0</v>
-      </c>
-      <c r="G12" s="28">
-        <v>0</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I12" s="37">
-        <v>0</v>
-      </c>
-      <c r="J12" s="38">
-        <v>0</v>
-      </c>
-      <c r="K12" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
-      <c r="C13" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="27">
-        <v>0</v>
-      </c>
-      <c r="E13" s="30">
-        <v>0</v>
-      </c>
-      <c r="F13" s="30">
-        <v>0</v>
-      </c>
-      <c r="G13" s="28">
-        <v>3</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I13" s="40">
-        <v>0</v>
-      </c>
-      <c r="J13" s="41">
-        <v>0</v>
-      </c>
-      <c r="K13" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="47"/>
-      <c r="C14" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="27">
-        <v>6</v>
-      </c>
-      <c r="E14" s="30">
-        <v>3</v>
-      </c>
-      <c r="F14" s="30">
-        <v>0</v>
-      </c>
-      <c r="G14" s="28">
-        <v>3</v>
-      </c>
-      <c r="H14" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="40">
-        <v>0</v>
-      </c>
-      <c r="J14" s="41">
-        <v>0</v>
-      </c>
-      <c r="K14" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
-      <c r="C15" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="27">
-        <v>7</v>
-      </c>
-      <c r="E15" s="30">
-        <v>0</v>
-      </c>
-      <c r="F15" s="30">
-        <v>0</v>
-      </c>
-      <c r="G15" s="28">
-        <v>0</v>
-      </c>
-      <c r="H15" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="40">
-        <v>0</v>
-      </c>
-      <c r="J15" s="41">
-        <v>0</v>
-      </c>
-      <c r="K15" s="42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" s="13" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="48"/>
-      <c r="C16" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="31">
-        <v>0</v>
-      </c>
-      <c r="E16" s="32">
-        <v>0</v>
-      </c>
-      <c r="F16" s="32">
-        <v>1</v>
-      </c>
-      <c r="G16" s="33">
-        <v>0</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I16" s="43">
-        <v>1</v>
-      </c>
-      <c r="J16" s="44">
-        <v>0</v>
-      </c>
-      <c r="K16" s="45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:24" s="22" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="B17" s="18"/>
-      <c r="C17" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="20">
-        <f>SUM(D4:D16)</f>
-        <v>140</v>
-      </c>
-      <c r="E17" s="20">
-        <f>SUM(E4:E16)</f>
-        <v>38</v>
-      </c>
-      <c r="F17" s="20">
-        <f>SUM(F4:F16)</f>
-        <v>8</v>
-      </c>
-      <c r="G17" s="20">
-        <f>SUM(G4:G16)</f>
-        <v>18</v>
-      </c>
-      <c r="H17" s="20">
-        <v>30</v>
-      </c>
-      <c r="I17" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="K17" s="21" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="2:24" s="25" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="23"/>
-      <c r="C18" s="19" t="s">
+    <row r="18" spans="2:24" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="20">
-        <v>30</v>
-      </c>
-      <c r="E18" s="19">
-        <v>25</v>
-      </c>
-      <c r="F18" s="20">
-        <v>30</v>
-      </c>
-      <c r="G18" s="20">
-        <v>30</v>
-      </c>
-      <c r="H18" s="19">
-        <v>15</v>
-      </c>
-      <c r="I18" s="21">
-        <v>0.25</v>
-      </c>
-      <c r="J18" s="21">
-        <v>0.25</v>
-      </c>
-      <c r="K18" s="21">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="19" spans="2:24" s="25" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="23"/>
-      <c r="C19" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="26">
-        <f>D18/13</f>
+      <c r="C18" s="40"/>
+      <c r="D18" s="17">
+        <f>D17/13</f>
         <v>2.3076923076923075</v>
       </c>
-      <c r="E19" s="26">
-        <f t="shared" ref="E19:G19" si="0">E18/13</f>
+      <c r="E18" s="17">
+        <f t="shared" ref="E18:G18" si="0">E17/13</f>
         <v>1.9230769230769231</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F18" s="17">
         <f t="shared" si="0"/>
         <v>2.3076923076923075</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G18" s="17">
         <f t="shared" si="0"/>
         <v>2.3076923076923075</v>
       </c>
-      <c r="H19" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="21">
+      <c r="H18" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="13">
         <v>0.25</v>
       </c>
-      <c r="J19" s="21">
+      <c r="J18" s="13">
         <v>0.25</v>
       </c>
-      <c r="K19" s="21">
+      <c r="K18" s="13">
         <v>0.25</v>
       </c>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
-      <c r="V19" s="24"/>
-      <c r="W19" s="24"/>
-      <c r="X19" s="24"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="15"/>
+      <c r="T18" s="15"/>
+      <c r="U18" s="15"/>
+      <c r="V18" s="15"/>
+      <c r="W18" s="15"/>
+      <c r="X18" s="15"/>
     </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="F26" s="35" t="s">
-        <v>28</v>
+    <row r="25" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="F25" s="26" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="I2:K2"/>
+  <mergeCells count="8">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D16">
+  <conditionalFormatting sqref="D3:D15">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$19/2"/>
-        <cfvo type="formula" val="$D$19"/>
+        <cfvo type="formula" val="$D$18/2"/>
+        <cfvo type="formula" val="$D$18"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
@@ -1719,36 +1750,36 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E16">
+  <conditionalFormatting sqref="E3:E15">
     <cfRule type="colorScale" priority="53">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$E$19/2"/>
-        <cfvo type="formula" val="$E$19"/>
+        <cfvo type="formula" val="$E$18/2"/>
+        <cfvo type="formula" val="$E$18"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F16">
+  <conditionalFormatting sqref="F3:F15">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$F$19/2"/>
-        <cfvo type="formula" val="$F$19"/>
+        <cfvo type="formula" val="$F$18/2"/>
+        <cfvo type="formula" val="$F$18"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G16">
+  <conditionalFormatting sqref="G3:G15">
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$G$19/2"/>
-        <cfvo type="formula" val="$G$19"/>
+        <cfvo type="formula" val="$G$18/2"/>
+        <cfvo type="formula" val="$G$18"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
@@ -1765,36 +1796,36 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I16">
+  <conditionalFormatting sqref="I3:I15">
     <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$I$19/2"/>
-        <cfvo type="formula" val="$I$19"/>
+        <cfvo type="formula" val="$I$18/2"/>
+        <cfvo type="formula" val="$I$18"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J16">
+  <conditionalFormatting sqref="J3:J15">
     <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$J$19/2"/>
-        <cfvo type="formula" val="$J$19"/>
+        <cfvo type="formula" val="$J$18/2"/>
+        <cfvo type="formula" val="$J$18"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K16">
+  <conditionalFormatting sqref="K3:K15">
     <cfRule type="colorScale" priority="59">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$K$19/2"/>
-        <cfvo type="formula" val="$K$19"/>
+        <cfvo type="formula" val="$K$18/2"/>
+        <cfvo type="formula" val="$K$18"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>

--- a/data/Heat map 5.xlsx
+++ b/data/Heat map 5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B7D5AB-7219-4E02-911F-43609664E511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{A20CC070-EDC6-4CDB-927C-3F513ED4C2FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC4FA62C-4147-4884-A9AB-CDD7F29E24A8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9DC939E2-9D2B-49F9-96FE-7432C9E71486}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9DC939E2-9D2B-49F9-96FE-7432C9E71486}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
@@ -154,11 +154,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -789,7 +790,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="90">
@@ -797,16 +798,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -823,19 +833,19 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -844,34 +854,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -884,6 +879,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -897,33 +895,12 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="3" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="11" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="3" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="3" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
@@ -939,47 +916,80 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -1011,35 +1021,26 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1382,687 +1383,687 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8" style="8" customWidth="1"/>
-    <col min="2" max="2" width="31.33203125" style="9" customWidth="1"/>
-    <col min="3" max="4" width="7.44140625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" style="24" customWidth="1"/>
-    <col min="6" max="10" width="7.44140625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="5.6640625" style="1" customWidth="1"/>
-    <col min="12" max="13" width="8.21875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8" style="11" customWidth="1"/>
+    <col min="2" max="2" width="31.36328125" style="12" customWidth="1"/>
+    <col min="3" max="4" width="7.453125" style="26" customWidth="1"/>
+    <col min="5" max="5" width="7.453125" style="27" customWidth="1"/>
+    <col min="6" max="10" width="7.453125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="5.6328125" style="1" customWidth="1"/>
+    <col min="12" max="13" width="8.1796875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="36"/>
-      <c r="B1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="79"/>
-    </row>
-    <row r="2" spans="1:13" s="89" customFormat="1" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81" t="s">
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="34"/>
+      <c r="B1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="82"/>
+    </row>
+    <row r="2" spans="1:13" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="35"/>
+      <c r="B2" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="C2" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="85" t="s">
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="85"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-    </row>
-    <row r="3" spans="1:13" s="5" customFormat="1" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="36"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="52" t="s">
+      <c r="I2" s="86"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" spans="1:13" s="8" customFormat="1" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="34"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="G3" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="54" t="s">
+      <c r="H3" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="55" t="s">
+      <c r="I3" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4" spans="1:13" s="8" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="73" t="s">
+      <c r="K3" s="6"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+    </row>
+    <row r="4" spans="1:13" s="11" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="56">
+      <c r="C4" s="48">
         <v>17</v>
       </c>
-      <c r="D4" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="57">
+      <c r="D4" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="49">
         <v>1</v>
       </c>
-      <c r="F4" s="57">
-        <v>0</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="48">
-        <v>0</v>
-      </c>
-      <c r="I4" s="25">
-        <v>0</v>
-      </c>
-      <c r="J4" s="26">
-        <v>0</v>
-      </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-    </row>
-    <row r="5" spans="1:13" s="8" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
-      <c r="B5" s="34" t="s">
+      <c r="F4" s="49">
+        <v>0</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="64">
+        <v>0</v>
+      </c>
+      <c r="I4" s="65">
+        <v>0</v>
+      </c>
+      <c r="J4" s="66">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+    </row>
+    <row r="5" spans="1:13" s="11" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="77"/>
+      <c r="B5" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="58">
+      <c r="C5" s="50">
         <v>23</v>
       </c>
-      <c r="D5" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="59">
-        <v>0</v>
-      </c>
-      <c r="F5" s="59">
-        <v>3</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="49">
+      <c r="D5" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="51">
+        <v>0</v>
+      </c>
+      <c r="F5" s="51">
+        <v>3</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="67">
         <v>0.28999999999999998</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="68">
         <v>0.14000000000000001</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="66">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-    </row>
-    <row r="6" spans="1:13" s="8" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="74"/>
-      <c r="B6" s="34" t="s">
+      <c r="K5" s="9"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+    </row>
+    <row r="6" spans="1:13" s="11" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="77"/>
+      <c r="B6" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="58">
+      <c r="C6" s="50">
         <v>19</v>
       </c>
-      <c r="D6" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="59">
-        <v>0</v>
-      </c>
-      <c r="F6" s="59">
+      <c r="D6" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="51">
+        <v>0</v>
+      </c>
+      <c r="F6" s="51">
         <v>1</v>
       </c>
-      <c r="G6" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="49">
-        <v>0</v>
-      </c>
-      <c r="I6" s="27">
-        <v>0</v>
-      </c>
-      <c r="J6" s="28">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-    </row>
-    <row r="7" spans="1:13" s="8" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="75"/>
-      <c r="B7" s="35" t="s">
+      <c r="G6" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="67">
+        <v>0</v>
+      </c>
+      <c r="I6" s="68">
+        <v>0</v>
+      </c>
+      <c r="J6" s="69">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+    </row>
+    <row r="7" spans="1:13" s="11" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="78"/>
+      <c r="B7" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="60">
-        <v>0</v>
-      </c>
-      <c r="D7" s="61">
+      <c r="C7" s="52">
+        <v>0</v>
+      </c>
+      <c r="D7" s="53">
         <v>14</v>
       </c>
-      <c r="E7" s="61">
-        <v>3</v>
-      </c>
-      <c r="F7" s="61">
-        <v>0</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="50">
+      <c r="E7" s="53">
+        <v>3</v>
+      </c>
+      <c r="F7" s="53">
+        <v>0</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="70">
         <v>0.43</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="71">
         <v>0.28999999999999998</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="72">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" spans="1:13" s="8" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="73" t="s">
+      <c r="K7" s="9"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+    </row>
+    <row r="8" spans="1:13" s="11" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="56">
+      <c r="C8" s="48">
         <v>18</v>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="49">
         <v>1</v>
       </c>
-      <c r="E8" s="57">
-        <v>3</v>
-      </c>
-      <c r="F8" s="57">
+      <c r="E8" s="49">
+        <v>3</v>
+      </c>
+      <c r="F8" s="49">
         <v>5</v>
       </c>
-      <c r="G8" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="48">
+      <c r="G8" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="64">
         <v>0.33</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="65">
         <v>0.33</v>
       </c>
-      <c r="J8" s="26">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-    </row>
-    <row r="9" spans="1:13" s="8" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="74"/>
-      <c r="B9" s="34" t="s">
+      <c r="J8" s="66">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+    </row>
+    <row r="9" spans="1:13" s="11" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="77"/>
+      <c r="B9" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="58">
+      <c r="C9" s="50">
         <v>43</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="51">
         <v>17</v>
       </c>
-      <c r="E9" s="59">
-        <v>0</v>
-      </c>
-      <c r="F9" s="59">
-        <v>3</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="49">
+      <c r="E9" s="51">
+        <v>0</v>
+      </c>
+      <c r="F9" s="51">
+        <v>3</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="67">
         <v>0.44</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="68">
         <v>0.44</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="72">
         <v>0.11</v>
       </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-    </row>
-    <row r="10" spans="1:13" s="8" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="74"/>
-      <c r="B10" s="34" t="s">
+      <c r="K9" s="9"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+    </row>
+    <row r="10" spans="1:13" s="11" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="77"/>
+      <c r="B10" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="58">
-        <v>0</v>
-      </c>
-      <c r="D10" s="59">
-        <v>3</v>
-      </c>
-      <c r="E10" s="59">
-        <v>0</v>
-      </c>
-      <c r="F10" s="59">
-        <v>0</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="49">
+      <c r="C10" s="50">
+        <v>0</v>
+      </c>
+      <c r="D10" s="51">
+        <v>3</v>
+      </c>
+      <c r="E10" s="51">
+        <v>0</v>
+      </c>
+      <c r="F10" s="51">
+        <v>0</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="67">
         <v>0.56999999999999995</v>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="68">
         <v>0.71</v>
       </c>
-      <c r="J10" s="28">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-    </row>
-    <row r="11" spans="1:13" s="8" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="75"/>
-      <c r="B11" s="35" t="s">
+      <c r="J10" s="69">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+    </row>
+    <row r="11" spans="1:13" s="11" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="78"/>
+      <c r="B11" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="60">
-        <v>0</v>
-      </c>
-      <c r="D11" s="61">
-        <v>0</v>
-      </c>
-      <c r="E11" s="61">
-        <v>0</v>
-      </c>
-      <c r="F11" s="61">
-        <v>0</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="H11" s="50">
-        <v>0</v>
-      </c>
-      <c r="I11" s="29">
-        <v>0</v>
-      </c>
-      <c r="J11" s="30">
-        <v>0</v>
-      </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-    </row>
-    <row r="12" spans="1:13" s="8" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="70" t="s">
+      <c r="C11" s="52">
+        <v>0</v>
+      </c>
+      <c r="D11" s="53">
+        <v>0</v>
+      </c>
+      <c r="E11" s="53">
+        <v>0</v>
+      </c>
+      <c r="F11" s="53">
+        <v>0</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="70">
+        <v>0</v>
+      </c>
+      <c r="I11" s="71">
+        <v>0</v>
+      </c>
+      <c r="J11" s="72">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+    </row>
+    <row r="12" spans="1:13" s="11" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="56">
+      <c r="C12" s="48">
         <v>7</v>
       </c>
-      <c r="D12" s="62">
-        <v>0</v>
-      </c>
-      <c r="E12" s="62">
-        <v>0</v>
-      </c>
-      <c r="F12" s="57">
-        <v>0</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="48">
-        <v>0</v>
-      </c>
-      <c r="I12" s="25">
-        <v>0</v>
-      </c>
-      <c r="J12" s="26">
-        <v>0</v>
-      </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-    </row>
-    <row r="13" spans="1:13" s="8" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="71"/>
-      <c r="B13" s="34" t="s">
+      <c r="D12" s="54">
+        <v>0</v>
+      </c>
+      <c r="E12" s="54">
+        <v>0</v>
+      </c>
+      <c r="F12" s="49">
+        <v>0</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="64">
+        <v>0</v>
+      </c>
+      <c r="I12" s="65">
+        <v>0</v>
+      </c>
+      <c r="J12" s="66">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+    </row>
+    <row r="13" spans="1:13" s="11" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="74"/>
+      <c r="B13" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="58">
-        <v>0</v>
-      </c>
-      <c r="D13" s="63">
-        <v>0</v>
-      </c>
-      <c r="E13" s="63">
-        <v>0</v>
-      </c>
-      <c r="F13" s="59">
-        <v>3</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="H13" s="49">
-        <v>0</v>
-      </c>
-      <c r="I13" s="27">
-        <v>0</v>
-      </c>
-      <c r="J13" s="28">
-        <v>0</v>
-      </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-    </row>
-    <row r="14" spans="1:13" s="8" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="71"/>
-      <c r="B14" s="34" t="s">
+      <c r="C13" s="50">
+        <v>0</v>
+      </c>
+      <c r="D13" s="55">
+        <v>0</v>
+      </c>
+      <c r="E13" s="55">
+        <v>0</v>
+      </c>
+      <c r="F13" s="51">
+        <v>3</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" s="67">
+        <v>0</v>
+      </c>
+      <c r="I13" s="68">
+        <v>0</v>
+      </c>
+      <c r="J13" s="69">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+    </row>
+    <row r="14" spans="1:13" s="11" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="74"/>
+      <c r="B14" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="58">
+      <c r="C14" s="50">
         <v>6</v>
       </c>
-      <c r="D14" s="63">
-        <v>3</v>
-      </c>
-      <c r="E14" s="63">
-        <v>0</v>
-      </c>
-      <c r="F14" s="59">
-        <v>3</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="49">
-        <v>0</v>
-      </c>
-      <c r="I14" s="27">
-        <v>0</v>
-      </c>
-      <c r="J14" s="28">
-        <v>0</v>
-      </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-    </row>
-    <row r="15" spans="1:13" s="8" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="71"/>
-      <c r="B15" s="34" t="s">
+      <c r="D14" s="55">
+        <v>3</v>
+      </c>
+      <c r="E14" s="55">
+        <v>0</v>
+      </c>
+      <c r="F14" s="51">
+        <v>3</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="67">
+        <v>0</v>
+      </c>
+      <c r="I14" s="68">
+        <v>0</v>
+      </c>
+      <c r="J14" s="69">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+    </row>
+    <row r="15" spans="1:13" s="11" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="74"/>
+      <c r="B15" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="58">
+      <c r="C15" s="50">
         <v>7</v>
       </c>
-      <c r="D15" s="63">
-        <v>0</v>
-      </c>
-      <c r="E15" s="63">
-        <v>0</v>
-      </c>
-      <c r="F15" s="59">
-        <v>0</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="49">
-        <v>0</v>
-      </c>
-      <c r="I15" s="27">
-        <v>0</v>
-      </c>
-      <c r="J15" s="28">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" spans="1:13" s="8" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="72"/>
-      <c r="B16" s="35" t="s">
+      <c r="D15" s="55">
+        <v>0</v>
+      </c>
+      <c r="E15" s="55">
+        <v>0</v>
+      </c>
+      <c r="F15" s="51">
+        <v>0</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="67">
+        <v>0</v>
+      </c>
+      <c r="I15" s="68">
+        <v>0</v>
+      </c>
+      <c r="J15" s="69">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+    </row>
+    <row r="16" spans="1:13" s="11" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="75"/>
+      <c r="B16" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="60">
-        <v>0</v>
-      </c>
-      <c r="D16" s="64">
-        <v>0</v>
-      </c>
-      <c r="E16" s="64">
+      <c r="C16" s="52">
+        <v>0</v>
+      </c>
+      <c r="D16" s="56">
+        <v>0</v>
+      </c>
+      <c r="E16" s="56">
         <v>1</v>
       </c>
-      <c r="F16" s="61">
-        <v>0</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="H16" s="50">
+      <c r="F16" s="53">
+        <v>0</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="H16" s="70">
         <v>1</v>
       </c>
-      <c r="I16" s="29">
-        <v>0</v>
-      </c>
-      <c r="J16" s="30">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-    </row>
-    <row r="17" spans="1:27" s="15" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A17" s="36"/>
-      <c r="B17" s="38" t="s">
+      <c r="I16" s="71">
+        <v>0</v>
+      </c>
+      <c r="J16" s="72">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+    </row>
+    <row r="17" spans="1:27" s="18" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A17" s="34"/>
+      <c r="B17" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="65">
+      <c r="C17" s="57">
         <f>SUM(C4:C16)</f>
         <v>140</v>
       </c>
-      <c r="D17" s="65">
+      <c r="D17" s="57">
         <f>SUM(D4:D16)</f>
         <v>38</v>
       </c>
-      <c r="E17" s="65">
+      <c r="E17" s="57">
         <f>SUM(E4:E16)</f>
         <v>8</v>
       </c>
-      <c r="F17" s="65">
+      <c r="F17" s="57">
         <f>SUM(F4:F16)</f>
         <v>18</v>
       </c>
-      <c r="G17" s="68">
+      <c r="G17" s="60">
         <v>30</v>
       </c>
-      <c r="H17" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="14"/>
-    </row>
-    <row r="18" spans="1:27" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
-      <c r="B18" s="41" t="s">
+      <c r="H17" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="17"/>
+    </row>
+    <row r="18" spans="1:27" s="20" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="36"/>
+      <c r="B18" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="65">
+      <c r="C18" s="57">
         <v>30</v>
       </c>
-      <c r="D18" s="66">
+      <c r="D18" s="58">
         <v>25</v>
       </c>
-      <c r="E18" s="65">
+      <c r="E18" s="57">
         <v>30</v>
       </c>
-      <c r="F18" s="65">
+      <c r="F18" s="57">
         <v>30</v>
       </c>
-      <c r="G18" s="69">
+      <c r="G18" s="61">
         <v>15</v>
       </c>
-      <c r="H18" s="42">
+      <c r="H18" s="62">
         <v>0.25</v>
       </c>
-      <c r="I18" s="42">
+      <c r="I18" s="62">
         <v>0.25</v>
       </c>
-      <c r="J18" s="43">
+      <c r="J18" s="63">
         <v>0.25</v>
       </c>
-      <c r="K18" s="13"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-    </row>
-    <row r="19" spans="1:27" s="17" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="37"/>
-      <c r="B19" s="44" t="s">
+      <c r="K18" s="16"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+    </row>
+    <row r="19" spans="1:27" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="36"/>
+      <c r="B19" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="67">
+      <c r="C19" s="59">
         <f>C18/13</f>
         <v>2.3076923076923075</v>
       </c>
-      <c r="D19" s="67">
+      <c r="D19" s="59">
         <f t="shared" ref="D19:F19" si="0">D18/13</f>
         <v>1.9230769230769231</v>
       </c>
-      <c r="E19" s="67">
+      <c r="E19" s="59">
         <f t="shared" si="0"/>
         <v>2.3076923076923075</v>
       </c>
-      <c r="F19" s="67">
+      <c r="F19" s="59">
         <f t="shared" si="0"/>
         <v>2.3076923076923075</v>
       </c>
-      <c r="G19" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="H19" s="46">
+      <c r="G19" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="H19" s="88">
         <v>0.25</v>
       </c>
-      <c r="I19" s="46">
+      <c r="I19" s="88">
         <v>0.25</v>
       </c>
-      <c r="J19" s="47">
+      <c r="J19" s="89">
         <v>0.25</v>
       </c>
-      <c r="K19" s="13"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="16"/>
-      <c r="Z19" s="16"/>
-      <c r="AA19" s="16"/>
-    </row>
-    <row r="21" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="10" t="s">
+      <c r="K19" s="16"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="19"/>
+      <c r="U19" s="19"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="19"/>
+      <c r="X19" s="19"/>
+      <c r="Y19" s="19"/>
+      <c r="Z19" s="19"/>
+      <c r="AA19" s="19"/>
+    </row>
+    <row r="21" spans="1:27" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="11"/>
-    </row>
-    <row r="22" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="12" t="s">
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="14"/>
+    </row>
+    <row r="22" spans="1:27" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="11"/>
-    </row>
-    <row r="23" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="12" t="s">
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="14"/>
+    </row>
+    <row r="23" spans="1:27" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="11"/>
-    </row>
-    <row r="24" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="12" t="s">
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="14"/>
+    </row>
+    <row r="24" spans="1:27" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:27" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B26" s="12"/>
+    <row r="25" spans="1:27" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="B26" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2190,10 +2191,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="88" orientation="landscape" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>